--- a/開發系統表分析表格.xlsx
+++ b/開發系統表分析表格.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my_code\AntiGravity_code\存檔備份\TCM-Meridian-11\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my_code\AntiGravity_code\TCM-Meridian\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233B5F25-D38A-494D-B3ED-74CACDC2BC17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5421480E-FF8E-4C9C-9083-F26D79AEA82D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="54">
   <si>
     <t>prompt_record_update</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -545,10 +545,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>教授 Query Expansion</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>V(只有即將更新的病歷)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -609,7 +605,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -757,12 +753,6 @@
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
-      <name val="標楷體"/>
-      <family val="4"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="標楷體"/>
       <family val="4"/>
       <charset val="136"/>
@@ -815,7 +805,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -835,7 +825,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1116,7 +1105,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64655AA0-732C-4848-9798-7F7FE16ECA47}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="42.3984375" style="14" bestFit="1" customWidth="1"/>
@@ -1127,12 +1116,11 @@
     <col min="6" max="6" width="35.8984375" style="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.3984375" style="18" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.796875" style="18" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26.796875" style="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="42.3984375" style="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.796875" style="14"/>
+    <col min="9" max="9" width="42.3984375" style="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.796875" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17">
+    <row r="1" spans="1:9" ht="17">
       <c r="A1" s="7"/>
       <c r="B1" s="9" t="s">
         <v>33</v>
@@ -1155,12 +1143,9 @@
       <c r="H1" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="J1" s="7"/>
-    </row>
-    <row r="2" spans="1:10" ht="17">
+      <c r="I1" s="7"/>
+    </row>
+    <row r="2" spans="1:9" ht="17">
       <c r="A2" s="7" t="s">
         <v>4</v>
       </c>
@@ -1183,14 +1168,13 @@
         <v>17</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="I2" s="16"/>
-      <c r="J2" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="17">
+    <row r="3" spans="1:9" ht="17">
       <c r="A3" s="7" t="s">
         <v>29</v>
       </c>
@@ -1209,12 +1193,11 @@
         <v>2</v>
       </c>
       <c r="H3" s="17"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="7" t="s">
+      <c r="I3" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="17">
+    <row r="4" spans="1:9" ht="17">
       <c r="A4" s="7" t="s">
         <v>30</v>
       </c>
@@ -1237,12 +1220,11 @@
       <c r="H4" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="16"/>
-      <c r="J4" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="17">
+    <row r="5" spans="1:9" ht="17">
       <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
@@ -1265,100 +1247,94 @@
       <c r="H5" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="I5" s="16"/>
-      <c r="J5" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="17">
+    <row r="6" spans="1:9" ht="17">
       <c r="A6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="17">
+      <c r="A7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="H7" s="17"/>
+      <c r="I7" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="17">
+      <c r="A8" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="I6" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="J6" s="7" t="s">
+      <c r="B8" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="H8" s="17"/>
+      <c r="I8" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="17">
-      <c r="A7" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="H7" s="17"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="17">
-      <c r="A8" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="H8" s="17"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="17">
+    <row r="9" spans="1:9" ht="17">
       <c r="A9" s="9" t="s">
         <v>28</v>
       </c>
@@ -1379,14 +1355,11 @@
       <c r="H9" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="I9" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="J9" s="9" t="s">
+      <c r="I9" s="9" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="17">
+    <row r="10" spans="1:9" ht="17">
       <c r="A10" s="9" t="s">
         <v>20</v>
       </c>
@@ -1401,22 +1374,21 @@
       </c>
       <c r="E10" s="15"/>
       <c r="F10" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="17">
+      <c r="A11" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="G10" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="I10" s="16"/>
-      <c r="J10" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="17">
-      <c r="A11" s="7" t="s">
-        <v>46</v>
       </c>
       <c r="B11" s="17"/>
       <c r="C11" s="15" t="s">
@@ -1427,21 +1399,20 @@
       </c>
       <c r="E11" s="15"/>
       <c r="F11" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G11" s="17"/>
       <c r="H11" s="17"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="17">
+      <c r="I11" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="17">
       <c r="A12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="16" t="s">
         <v>48</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>49</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>2</v>
@@ -1455,14 +1426,13 @@
       </c>
       <c r="G12" s="17"/>
       <c r="H12" s="17"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="17">
+      <c r="I12" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="17">
       <c r="A13" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>2</v>
@@ -1481,9 +1451,8 @@
         <v>2</v>
       </c>
       <c r="H13" s="17"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="7" t="s">
-        <v>54</v>
+      <c r="I13" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
